--- a/DCF-Excel&EquityNote/AMD_DCF_Valuation.xlsx
+++ b/DCF-Excel&EquityNote/AMD_DCF_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DCF\Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D534FCC-CE37-42DF-9CC4-E977761747BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F42E932-0B58-4AED-BCE0-AEAAE0E18CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="232">
   <si>
     <t>ADVANCED MICRO DEVICES, INC. (AMD)</t>
   </si>
@@ -689,9 +689,6 @@
     <t>Notes:</t>
   </si>
   <si>
-    <t>• OpenAI warrant (up to 160M shares at $0.01) excluded from base case; potential dilution.</t>
-  </si>
-  <si>
     <t>• SBC treated as cash expense (subtracted from FCF) per conservative methodology.</t>
   </si>
   <si>
@@ -735,6 +732,9 @@
   </si>
   <si>
     <t>FY2025 Operating Income ($M):</t>
+  </si>
+  <si>
+    <t>• OpenAI warrant (up to 160M shares at $0.01) included as potential dilution.</t>
   </si>
 </sst>
 </file>
@@ -747,7 +747,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="170" formatCode="#,##0.00;\(#,##0.00\)"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -1090,27 +1090,27 @@
     <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="169" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="170" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1426,24 +1426,24 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
     </row>
     <row r="3" spans="2:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
     </row>
     <row r="5" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
@@ -1454,19 +1454,19 @@
       <c r="B6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
     </row>
     <row r="7" spans="2:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
     </row>
     <row r="9" spans="2:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="E10" s="4">
         <f>'DCF Valuation'!C36</f>
-        <v>71.949722580853603</v>
+        <v>58.15697677729311</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>14</v>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E11" s="5">
         <f>'DCF Valuation'!C30</f>
-        <v>110407.7461422765</v>
+        <v>97147.930292018427</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="E12" s="5">
         <f>'DCF Valuation'!C33</f>
-        <v>117709.7461422765</v>
+        <v>104449.93029201843</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>16</v>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="E13" s="6">
         <f>WACC!C24</f>
-        <v>0.13789625369489783</v>
+        <v>0.1378818853617787</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>17</v>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="E14" s="7">
         <f>Assumptions!C45</f>
-        <v>0.03</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>18</v>
@@ -1574,7 +1574,7 @@
         <v>11</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E16" s="8">
         <f>Historicals!G24</f>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="E17" s="8">
         <f>Assumptions!C41</f>
-        <v>1636</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="38" spans="2:2" ht="24" x14ac:dyDescent="0.25">
@@ -1625,14 +1625,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
@@ -1675,14 +1675,14 @@
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
@@ -1733,7 +1733,7 @@
         <v>42</v>
       </c>
       <c r="C10" s="14">
-        <v>7609</v>
+        <v>8505</v>
       </c>
       <c r="D10" s="14">
         <v>11550</v>
@@ -1752,9 +1752,7 @@
       <c r="B11" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="14">
-        <v>509</v>
-      </c>
+      <c r="C11" s="14"/>
       <c r="D11" s="14">
         <v>1448</v>
       </c>
@@ -1774,7 +1772,7 @@
       </c>
       <c r="C12" s="19">
         <f>C8-C10-C11</f>
-        <v>8316</v>
+        <v>7929</v>
       </c>
       <c r="D12" s="19">
         <f>D8-D10-D11</f>
@@ -1799,7 +1797,7 @@
       </c>
       <c r="C13" s="17">
         <f>C12/C8</f>
-        <v>0.50602409638554213</v>
+        <v>0.48247535596933189</v>
       </c>
       <c r="D13" s="17">
         <f>D12/D8</f>
@@ -1819,21 +1817,21 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="55" t="s">
+      <c r="B15" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>47</v>
       </c>
       <c r="C16" s="14">
-        <v>4407</v>
+        <v>2845</v>
       </c>
       <c r="D16" s="14">
         <v>5005</v>
@@ -1854,7 +1852,7 @@
       </c>
       <c r="C17" s="17">
         <f>C16/C8</f>
-        <v>0.26816356334428626</v>
+        <v>0.17311670926128758</v>
       </c>
       <c r="D17" s="17">
         <f>D16/D8</f>
@@ -1878,7 +1876,7 @@
         <v>49</v>
       </c>
       <c r="C18" s="14">
-        <v>1905</v>
+        <v>1448</v>
       </c>
       <c r="D18" s="14">
         <v>2336</v>
@@ -1899,7 +1897,7 @@
       </c>
       <c r="C19" s="17">
         <f>C18/C8</f>
-        <v>0.11591821832785688</v>
+        <v>8.81100158208592E-2</v>
       </c>
       <c r="D19" s="17">
         <f>D18/D8</f>
@@ -1922,9 +1920,7 @@
       <c r="B20" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="14">
-        <v>525</v>
-      </c>
+      <c r="C20" s="14"/>
       <c r="D20" s="14">
         <v>2100</v>
       </c>
@@ -1963,7 +1959,7 @@
         <v>53</v>
       </c>
       <c r="C22" s="14">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="D22" s="14">
         <v>102</v>
@@ -1984,7 +1980,7 @@
       </c>
       <c r="C23" s="19">
         <f>C16+C18+C20+C21-C22</f>
-        <v>6790</v>
+        <v>4281</v>
       </c>
       <c r="D23" s="19">
         <f>D16+D18+D20+D21-D22</f>
@@ -2009,7 +2005,7 @@
       </c>
       <c r="C24" s="19">
         <f>C12-C23</f>
-        <v>1526</v>
+        <v>3648</v>
       </c>
       <c r="D24" s="19">
         <f>D12-D23</f>
@@ -2034,7 +2030,7 @@
       </c>
       <c r="C25" s="17">
         <f>C24/C8</f>
-        <v>9.2856273579165149E-2</v>
+        <v>0.22197882438846295</v>
       </c>
       <c r="D25" s="17">
         <f>D24/D8</f>
@@ -2058,7 +2054,7 @@
         <v>57</v>
       </c>
       <c r="C26" s="14">
-        <v>250</v>
+        <v>34</v>
       </c>
       <c r="D26" s="14">
         <v>88</v>
@@ -2078,7 +2074,7 @@
         <v>58</v>
       </c>
       <c r="C27" s="14">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D27" s="14">
         <v>8</v>
@@ -2099,7 +2095,7 @@
       </c>
       <c r="C28" s="19">
         <f>C24-C26+C27</f>
-        <v>1301</v>
+        <v>3669</v>
       </c>
       <c r="D28" s="19">
         <f>D24-D26+D27</f>
@@ -2123,7 +2119,7 @@
         <v>60</v>
       </c>
       <c r="C29" s="14">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="D29" s="14">
         <v>122</v>
@@ -2144,7 +2140,7 @@
       </c>
       <c r="C30" s="17">
         <f>C29/C28</f>
-        <v>0.40353574173712531</v>
+        <v>0.13982011447260834</v>
       </c>
       <c r="D30" s="17">
         <f>D29/D28</f>
@@ -2213,7 +2209,7 @@
         <v>64</v>
       </c>
       <c r="C33" s="20">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="D33" s="20">
         <v>0.84</v>
@@ -2249,21 +2245,21 @@
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B36" s="55" t="s">
+      <c r="B36" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="54"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="54"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="54"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>67</v>
       </c>
       <c r="C37" s="14">
-        <v>2730</v>
+        <v>3521</v>
       </c>
       <c r="D37" s="14">
         <v>3565</v>
@@ -2283,7 +2279,7 @@
         <v>68</v>
       </c>
       <c r="C38" s="14">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="D38" s="14">
         <v>450</v>
@@ -2304,7 +2300,7 @@
       </c>
       <c r="C39" s="19">
         <f>C37-C38</f>
-        <v>2444</v>
+        <v>3220</v>
       </c>
       <c r="D39" s="19">
         <f>D37-D38</f>
@@ -2329,7 +2325,7 @@
       </c>
       <c r="C40" s="17">
         <f>C39/C8</f>
-        <v>0.14871607642691981</v>
+        <v>0.19593525617622004</v>
       </c>
       <c r="D40" s="17">
         <f>D39/D8</f>
@@ -2354,7 +2350,7 @@
       </c>
       <c r="C41" s="17">
         <f>C38/C8</f>
-        <v>1.7402945113788489E-2</v>
+        <v>1.8315686990385785E-2</v>
       </c>
       <c r="D41" s="17">
         <f>D38/D8</f>
@@ -2398,7 +2394,7 @@
         <v>73</v>
       </c>
       <c r="C43" s="14">
-        <v>1256</v>
+        <v>379</v>
       </c>
       <c r="D43" s="14">
         <v>1081</v>
@@ -2419,7 +2415,7 @@
       </c>
       <c r="C44" s="17">
         <f>C43/C8</f>
-        <v>7.6426919800413773E-2</v>
+        <v>2.3061944748691738E-2</v>
       </c>
       <c r="D44" s="17">
         <f>D43/D8</f>
@@ -2439,21 +2435,21 @@
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B46" s="55" t="s">
+      <c r="B46" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="C46" s="54"/>
-      <c r="D46" s="54"/>
-      <c r="E46" s="54"/>
-      <c r="F46" s="54"/>
-      <c r="G46" s="54"/>
+      <c r="C46" s="55"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="55"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>76</v>
       </c>
       <c r="C47" s="14">
-        <v>3585</v>
+        <v>2535</v>
       </c>
       <c r="D47" s="14">
         <v>4835</v>
@@ -2473,10 +2469,10 @@
         <v>77</v>
       </c>
       <c r="C48" s="14">
-        <v>1250</v>
+        <v>1073</v>
       </c>
       <c r="D48" s="14">
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="E48" s="14">
         <v>1840</v>
@@ -2494,11 +2490,11 @@
       </c>
       <c r="C49" s="19">
         <f>C47+C48</f>
-        <v>4835</v>
+        <v>3608</v>
       </c>
       <c r="D49" s="19">
         <f>D47+D48</f>
-        <v>4835</v>
+        <v>5855</v>
       </c>
       <c r="E49" s="19">
         <f>E47+E48</f>
@@ -2518,7 +2514,7 @@
         <v>79</v>
       </c>
       <c r="C50" s="14">
-        <v>1300</v>
+        <v>313</v>
       </c>
       <c r="D50" s="14">
         <v>3200</v>
@@ -2539,11 +2535,11 @@
       </c>
       <c r="C51" s="19">
         <f>C49-C50</f>
-        <v>3535</v>
+        <v>3295</v>
       </c>
       <c r="D51" s="19">
         <f>D49-D50</f>
-        <v>1635</v>
+        <v>2655</v>
       </c>
       <c r="E51" s="19">
         <f>E49-E50</f>
@@ -2563,7 +2559,7 @@
         <v>81</v>
       </c>
       <c r="C52" s="14">
-        <v>9478</v>
+        <v>7497</v>
       </c>
       <c r="D52" s="14">
         <v>54750</v>
@@ -2579,21 +2575,21 @@
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B54" s="55" t="s">
+      <c r="B54" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="C54" s="54"/>
-      <c r="D54" s="54"/>
-      <c r="E54" s="54"/>
-      <c r="F54" s="54"/>
-      <c r="G54" s="54"/>
+      <c r="C54" s="55"/>
+      <c r="D54" s="55"/>
+      <c r="E54" s="55"/>
+      <c r="F54" s="55"/>
+      <c r="G54" s="55"/>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>83</v>
       </c>
       <c r="C55" s="14">
-        <v>2630</v>
+        <v>3694</v>
       </c>
       <c r="D55" s="14">
         <v>6043</v>
@@ -2613,7 +2609,7 @@
         <v>84</v>
       </c>
       <c r="C56" s="14">
-        <v>6600</v>
+        <v>6997</v>
       </c>
       <c r="D56" s="14">
         <v>6201</v>
@@ -2632,8 +2628,8 @@
       <c r="B57" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C57" s="21" t="s">
-        <v>85</v>
+      <c r="C57" s="14">
+        <v>5607</v>
       </c>
       <c r="D57" s="14">
         <v>6805</v>
@@ -2673,7 +2669,7 @@
         <v>88</v>
       </c>
       <c r="C59" s="14">
-        <v>1160</v>
+        <v>246</v>
       </c>
       <c r="D59" s="14">
         <v>4552</v>
@@ -2694,7 +2690,7 @@
       </c>
       <c r="C60" s="17">
         <f>C55/C8</f>
-        <v>0.16003407569672629</v>
+        <v>0.22477789947669466</v>
       </c>
       <c r="D60" s="17">
         <f>D55/D8</f>
@@ -2748,15 +2744,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
     </row>
     <row r="4" spans="2:8" ht="24" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
@@ -2784,22 +2780,22 @@
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
         <v>96</v>
       </c>
       <c r="D8" s="22">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="E8" s="22">
         <v>0.24</v>
@@ -2825,22 +2821,22 @@
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="55" t="s">
+      <c r="B12" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
         <v>100</v>
       </c>
       <c r="D13" s="22">
-        <v>0.51</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="E13" s="22">
         <v>0.52</v>
@@ -2852,7 +2848,7 @@
         <v>0.53</v>
       </c>
       <c r="H13" s="22">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="24" x14ac:dyDescent="0.25">
@@ -2865,19 +2861,19 @@
         <v>102</v>
       </c>
       <c r="D15" s="22">
+        <v>0.23</v>
+      </c>
+      <c r="E15" s="22">
         <v>0.22</v>
       </c>
-      <c r="E15" s="22">
+      <c r="F15" s="22">
+        <v>0.21</v>
+      </c>
+      <c r="G15" s="22">
         <v>0.2</v>
       </c>
-      <c r="F15" s="22">
-        <v>0.19</v>
-      </c>
-      <c r="G15" s="22">
-        <v>0.18</v>
-      </c>
       <c r="H15" s="22">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="24" x14ac:dyDescent="0.25">
@@ -2893,16 +2889,16 @@
         <v>0.11</v>
       </c>
       <c r="E17" s="22">
+        <v>0.105</v>
+      </c>
+      <c r="F17" s="22">
         <v>0.1</v>
       </c>
-      <c r="F17" s="22">
+      <c r="G17" s="22">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="G17" s="22">
+      <c r="H17" s="22">
         <v>0.09</v>
-      </c>
-      <c r="H17" s="22">
-        <v>8.5000000000000006E-2</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="24" x14ac:dyDescent="0.25">
@@ -2936,34 +2932,34 @@
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="55" t="s">
+      <c r="B22" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="13" t="s">
         <v>109</v>
       </c>
       <c r="D23" s="22">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="E23" s="22">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="F23" s="22">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="G23" s="22">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H23" s="22">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="24" x14ac:dyDescent="0.25">
@@ -3067,15 +3063,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="55" t="s">
+      <c r="B33" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="55"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="13" t="s">
@@ -3084,13 +3080,13 @@
       <c r="C34" s="24">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="D34" s="53" t="s">
+      <c r="D34" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="E34" s="54"/>
-      <c r="F34" s="54"/>
-      <c r="G34" s="54"/>
-      <c r="H34" s="54"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="55"/>
+      <c r="H34" s="55"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="13" t="s">
@@ -3099,28 +3095,28 @@
       <c r="C35" s="24">
         <v>5.5E-2</v>
       </c>
-      <c r="D35" s="53" t="s">
+      <c r="D35" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="E35" s="54"/>
-      <c r="F35" s="54"/>
-      <c r="G35" s="54"/>
-      <c r="H35" s="54"/>
+      <c r="E35" s="55"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="55"/>
+      <c r="H35" s="55"/>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C36" s="61">
+      <c r="C36" s="53">
         <v>1.75</v>
       </c>
-      <c r="D36" s="53" t="s">
+      <c r="D36" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="E36" s="54"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="54"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="13" t="s">
@@ -3129,13 +3125,13 @@
       <c r="C37" s="24">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="D37" s="53" t="s">
+      <c r="D37" s="58" t="s">
         <v>126</v>
       </c>
-      <c r="E37" s="54"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="54"/>
-      <c r="H37" s="54"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="13" t="s">
@@ -3144,13 +3140,13 @@
       <c r="C38" s="23">
         <v>385800</v>
       </c>
-      <c r="D38" s="53" t="s">
+      <c r="D38" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="E38" s="54"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="54"/>
-      <c r="H38" s="54"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="13" t="s">
@@ -3159,13 +3155,13 @@
       <c r="C39" s="23">
         <v>3250</v>
       </c>
-      <c r="D39" s="53" t="s">
+      <c r="D39" s="58" t="s">
         <v>130</v>
       </c>
-      <c r="E39" s="54"/>
-      <c r="F39" s="54"/>
-      <c r="G39" s="54"/>
-      <c r="H39" s="54"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="13" t="s">
@@ -3174,46 +3170,46 @@
       <c r="C40" s="23">
         <v>10552</v>
       </c>
-      <c r="D40" s="53" t="s">
+      <c r="D40" s="58" t="s">
         <v>132</v>
       </c>
-      <c r="E40" s="54"/>
-      <c r="F40" s="54"/>
-      <c r="G40" s="54"/>
-      <c r="H40" s="54"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="13" t="s">
         <v>65</v>
       </c>
       <c r="C41" s="23">
-        <v>1636</v>
-      </c>
-      <c r="D41" s="53" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D41" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="E41" s="54"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="54"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="55" t="s">
+      <c r="B44" s="56" t="s">
         <v>134</v>
       </c>
-      <c r="C44" s="54"/>
-      <c r="D44" s="54"/>
-      <c r="E44" s="54"/>
-      <c r="F44" s="54"/>
-      <c r="G44" s="54"/>
-      <c r="H44" s="54"/>
+      <c r="C44" s="55"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="55"/>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B45" s="13" t="s">
         <v>135</v>
       </c>
       <c r="C45" s="22">
-        <v>0.03</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.25">
@@ -3223,6 +3219,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D40:H40"/>
     <mergeCell ref="B12:H12"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="D37:H37"/>
@@ -3232,11 +3233,6 @@
     <mergeCell ref="D36:H36"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="B44:H44"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3254,11 +3250,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="12" t="s">
@@ -3272,11 +3268,11 @@
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="61"/>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="15" t="s">
@@ -3327,11 +3323,11 @@
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="59" t="s">
         <v>149</v>
       </c>
-      <c r="C12" s="59"/>
-      <c r="D12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="61"/>
     </row>
     <row r="13" spans="2:4" ht="24" x14ac:dyDescent="0.25">
       <c r="B13" s="15" t="s">
@@ -3351,7 +3347,7 @@
       </c>
       <c r="C14" s="28">
         <f>Assumptions!D23</f>
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>153</v>
@@ -3363,15 +3359,15 @@
       </c>
       <c r="C15" s="27">
         <f>C13*(1-C14)</f>
-        <v>3.6549999999999999E-2</v>
+        <v>3.483E-2</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="59" t="s">
         <v>155</v>
       </c>
-      <c r="C17" s="59"/>
-      <c r="D17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="61"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
@@ -3430,7 +3426,7 @@
       </c>
       <c r="C24" s="33">
         <f>C21*C10+C22*C15</f>
-        <v>0.13789625369489783</v>
+        <v>0.1378818853617787</v>
       </c>
       <c r="D24" s="34" t="s">
         <v>164</v>
@@ -3458,14 +3454,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="54" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
@@ -3488,14 +3484,14 @@
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="55" t="s">
+      <c r="B6" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
@@ -3503,23 +3499,23 @@
       </c>
       <c r="C7" s="35">
         <f>Historicals!G8*(1+Assumptions!D8)</f>
-        <v>45723.48</v>
+        <v>47109.039999999994</v>
       </c>
       <c r="D7" s="35">
         <f>C7*(1+Assumptions!E8)</f>
-        <v>56697.1152</v>
+        <v>58415.209599999995</v>
       </c>
       <c r="E7" s="35">
         <f>D7*(1+Assumptions!F8)</f>
-        <v>66902.595935999998</v>
+        <v>68929.947327999995</v>
       </c>
       <c r="F7" s="35">
         <f>E7*(1+Assumptions!G8)</f>
-        <v>76268.959367040006</v>
+        <v>78580.139953920007</v>
       </c>
       <c r="G7" s="35">
         <f>F7*(1+Assumptions!H8)</f>
-        <v>84658.544897414409</v>
+        <v>87223.955348851217</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -3528,7 +3524,7 @@
       </c>
       <c r="C8" s="17">
         <f>C7/Historicals!G8-1</f>
-        <v>0.32000000000000006</v>
+        <v>0.35999999999999988</v>
       </c>
       <c r="D8" s="17">
         <f>D7/C7-1</f>
@@ -3553,23 +3549,23 @@
       </c>
       <c r="C9" s="35">
         <f>C7*Assumptions!D13</f>
-        <v>23318.974800000004</v>
+        <v>24261.155599999998</v>
       </c>
       <c r="D9" s="35">
         <f>D7*Assumptions!E13</f>
-        <v>29482.499904</v>
+        <v>30375.908991999997</v>
       </c>
       <c r="E9" s="35">
         <f>E7*Assumptions!F13</f>
-        <v>35123.862866399999</v>
+        <v>36188.222347199997</v>
       </c>
       <c r="F9" s="35">
         <f>F7*Assumptions!G13</f>
-        <v>40422.548464531203</v>
+        <v>41647.474175577605</v>
       </c>
       <c r="G9" s="35">
         <f>G7*Assumptions!H13</f>
-        <v>44869.028795629638</v>
+        <v>47100.935888379659</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -3578,7 +3574,7 @@
       </c>
       <c r="C10" s="17">
         <f>C9/C7</f>
-        <v>0.51</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="D10" s="17">
         <f>D9/D7</f>
@@ -3594,7 +3590,7 @@
       </c>
       <c r="G10" s="17">
         <f>G9/G7</f>
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
@@ -3603,23 +3599,23 @@
       </c>
       <c r="C11" s="14">
         <f>C7*Assumptions!D15</f>
-        <v>10059.1656</v>
+        <v>10835.079199999998</v>
       </c>
       <c r="D11" s="14">
         <f>D7*Assumptions!E15</f>
-        <v>11339.423040000001</v>
+        <v>12851.346111999999</v>
       </c>
       <c r="E11" s="14">
         <f>E7*Assumptions!F15</f>
-        <v>12711.493227839999</v>
+        <v>14475.288938879998</v>
       </c>
       <c r="F11" s="14">
         <f>F7*Assumptions!G15</f>
-        <v>13728.4126860672</v>
+        <v>15716.027990784001</v>
       </c>
       <c r="G11" s="14">
         <f>G7*Assumptions!H15</f>
-        <v>14391.952632560451</v>
+        <v>17444.791069770243</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -3628,23 +3624,23 @@
       </c>
       <c r="C12" s="14">
         <f>C7*Assumptions!D17</f>
-        <v>5029.5828000000001</v>
+        <v>5181.9943999999996</v>
       </c>
       <c r="D12" s="14">
         <f>D7*Assumptions!E17</f>
-        <v>5669.7115200000007</v>
+        <v>6133.5970079999988</v>
       </c>
       <c r="E12" s="14">
         <f>E7*Assumptions!F17</f>
-        <v>6355.7466139199996</v>
+        <v>6892.9947327999998</v>
       </c>
       <c r="F12" s="14">
         <f>F7*Assumptions!G17</f>
-        <v>6864.2063430336002</v>
+        <v>7465.113295622401</v>
       </c>
       <c r="G12" s="14">
         <f>G7*Assumptions!H17</f>
-        <v>7195.9763162802255</v>
+        <v>7850.1559813966096</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -3678,23 +3674,23 @@
       </c>
       <c r="C14" s="19">
         <f>C9-C11-C12-C13</f>
-        <v>6077.2264000000032</v>
+        <v>6091.0820000000003</v>
       </c>
       <c r="D14" s="19">
         <f>D9-D11-D12-D13</f>
-        <v>10437.365343999998</v>
+        <v>9354.9658719999989</v>
       </c>
       <c r="E14" s="19">
         <f>E9-E11-E12-E13</f>
-        <v>14133.623024639997</v>
+        <v>12896.938675520001</v>
       </c>
       <c r="F14" s="19">
         <f>F9-F11-F12-F13</f>
-        <v>18138.9294354304</v>
+        <v>16775.332889171201</v>
       </c>
       <c r="G14" s="19">
         <f>G9-G11-G12-G13</f>
-        <v>21827.099846788959</v>
+        <v>20351.988837212808</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
@@ -3703,23 +3699,23 @@
       </c>
       <c r="C15" s="17">
         <f>C14/C7</f>
-        <v>0.13291259545423934</v>
+        <v>0.12929751911734991</v>
       </c>
       <c r="D15" s="17">
         <f>D14/D7</f>
-        <v>0.18408988371246088</v>
+        <v>0.16014606360327088</v>
       </c>
       <c r="E15" s="17">
         <f>E14/E7</f>
-        <v>0.21125672071320561</v>
+        <v>0.18710211128046436</v>
       </c>
       <c r="F15" s="17">
         <f>F14/F7</f>
-        <v>0.23782846371533456</v>
+        <v>0.21348056772370708</v>
       </c>
       <c r="G15" s="17">
         <f>G14/G7</f>
-        <v>0.25782512412938469</v>
+        <v>0.23333026753734407</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -3728,23 +3724,23 @@
       </c>
       <c r="C16" s="14">
         <f>C14*Assumptions!D23</f>
-        <v>911.5839600000005</v>
+        <v>1157.30558</v>
       </c>
       <c r="D16" s="14">
         <f>D14*Assumptions!E23</f>
-        <v>1565.6048015999997</v>
+        <v>1777.4435156799998</v>
       </c>
       <c r="E16" s="14">
         <f>E14*Assumptions!F23</f>
-        <v>2120.0434536959997</v>
+        <v>2450.4183483488005</v>
       </c>
       <c r="F16" s="14">
         <f>F14*Assumptions!G23</f>
-        <v>2720.83941531456</v>
+        <v>3187.3132489425284</v>
       </c>
       <c r="G16" s="14">
         <f>G14*Assumptions!H23</f>
-        <v>3274.0649770183436</v>
+        <v>3866.8778790704337</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -3753,34 +3749,34 @@
       </c>
       <c r="C17" s="19">
         <f>C14-C16</f>
-        <v>5165.6424400000024</v>
+        <v>4933.7764200000001</v>
       </c>
       <c r="D17" s="19">
         <f>D14-D16</f>
-        <v>8871.7605423999976</v>
+        <v>7577.5223563199988</v>
       </c>
       <c r="E17" s="19">
         <f>E14-E16</f>
-        <v>12013.579570943997</v>
+        <v>10446.520327171202</v>
       </c>
       <c r="F17" s="19">
         <f>F14-F16</f>
-        <v>15418.09002011584</v>
+        <v>13588.019640228673</v>
       </c>
       <c r="G17" s="19">
         <f>G14-G16</f>
-        <v>18553.034869770614</v>
+        <v>16485.110958142373</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="56" t="s">
         <v>173</v>
       </c>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
@@ -3813,23 +3809,23 @@
       </c>
       <c r="C21" s="14">
         <f>C7*Assumptions!D27</f>
-        <v>1143.0870000000002</v>
+        <v>1177.7259999999999</v>
       </c>
       <c r="D21" s="14">
         <f>D7*Assumptions!E27</f>
-        <v>1417.4278800000002</v>
+        <v>1460.38024</v>
       </c>
       <c r="E21" s="14">
         <f>E7*Assumptions!F27</f>
-        <v>1672.5648983999999</v>
+        <v>1723.2486832</v>
       </c>
       <c r="F21" s="14">
         <f>F7*Assumptions!G27</f>
-        <v>1906.7239841760002</v>
+        <v>1964.5034988480002</v>
       </c>
       <c r="G21" s="14">
         <f>G7*Assumptions!H27</f>
-        <v>2116.4636224353603</v>
+        <v>2180.5988837212803</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -3838,23 +3834,23 @@
       </c>
       <c r="C22" s="14">
         <f>C7*Assumptions!D28</f>
-        <v>2286.1740000000004</v>
+        <v>2355.4519999999998</v>
       </c>
       <c r="D22" s="14">
         <f>D7*Assumptions!E28</f>
-        <v>2721.4615296000002</v>
+        <v>2803.9300607999999</v>
       </c>
       <c r="E22" s="14">
         <f>E7*Assumptions!F28</f>
-        <v>3010.6168171199997</v>
+        <v>3101.8476297599996</v>
       </c>
       <c r="F22" s="14">
         <f>F7*Assumptions!G28</f>
-        <v>3279.5652527827201</v>
+        <v>3378.9460180185602</v>
       </c>
       <c r="G22" s="14">
         <f>G7*Assumptions!H28</f>
-        <v>3386.3417958965765</v>
+        <v>3488.9582139540489</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -3863,23 +3859,23 @@
       </c>
       <c r="C23" s="14">
         <f>C7*Assumptions!D25</f>
-        <v>1371.7044000000001</v>
+        <v>1413.2711999999997</v>
       </c>
       <c r="D23" s="14">
         <f>D7*Assumptions!E25</f>
-        <v>1700.913456</v>
+        <v>1752.4562879999999</v>
       </c>
       <c r="E23" s="14">
         <f>E7*Assumptions!F25</f>
-        <v>1873.2726862079999</v>
+        <v>1930.0385251839998</v>
       </c>
       <c r="F23" s="14">
         <f>F7*Assumptions!G25</f>
-        <v>1906.7239841760002</v>
+        <v>1964.5034988480002</v>
       </c>
       <c r="G23" s="14">
         <f>G7*Assumptions!H25</f>
-        <v>2116.4636224353603</v>
+        <v>2180.5988837212803</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -3888,23 +3884,23 @@
       </c>
       <c r="C24" s="14">
         <f>(C7-Historicals!G8)*Assumptions!D30</f>
-        <v>1662.6720000000005</v>
+        <v>1870.5059999999989</v>
       </c>
       <c r="D24" s="14">
         <f>(D7-C7)*Assumptions!E30</f>
-        <v>1316.8362239999997</v>
+        <v>1356.740352</v>
       </c>
       <c r="E24" s="14">
         <f>(E7-D7)*Assumptions!F30</f>
-        <v>1020.5480735999998</v>
+        <v>1051.4737728</v>
       </c>
       <c r="F24" s="14">
         <f>(F7-E7)*Assumptions!G30</f>
-        <v>749.30907448320067</v>
+        <v>772.01541007360095</v>
       </c>
       <c r="G24" s="14">
         <f>(G7-F7)*Assumptions!H30</f>
-        <v>671.16684242995223</v>
+        <v>691.50523159449688</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
@@ -3913,23 +3909,23 @@
       </c>
       <c r="C25" s="36">
         <f>C17+C20+C21-C22-C23-C24</f>
-        <v>3141.1790400000009</v>
+        <v>2625.2732200000032</v>
       </c>
       <c r="D25" s="36">
         <f>D17+D20+D21-D22-D23-D24</f>
-        <v>6585.9772127999977</v>
+        <v>5160.7758955199997</v>
       </c>
       <c r="E25" s="36">
         <f>E17+E20+E21-E22-E23-E24</f>
-        <v>9704.7068924159994</v>
+        <v>8009.4090826272022</v>
       </c>
       <c r="F25" s="36">
         <f>F17+F20+F21-F22-F23-F24</f>
-        <v>13080.215692849917</v>
+        <v>11128.05821213651</v>
       </c>
       <c r="G25" s="36">
         <f>G17+G20+G21-G22-G23-G24</f>
-        <v>15949.526231444086</v>
+        <v>13758.647512593823</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -3938,23 +3934,23 @@
       </c>
       <c r="C26" s="17">
         <f>C25/C7</f>
-        <v>6.869947431822776E-2</v>
+        <v>5.5727589014762421E-2</v>
       </c>
       <c r="D26" s="17">
         <f>D25/D7</f>
-        <v>0.11616071099151792</v>
+        <v>8.8346441463765635E-2</v>
       </c>
       <c r="E26" s="17">
         <f>E25/E7</f>
-        <v>0.14505725460488356</v>
+        <v>0.11619636156857623</v>
       </c>
       <c r="F26" s="17">
         <f>F25/F7</f>
-        <v>0.17150116903919099</v>
+        <v>0.14161413072898685</v>
       </c>
       <c r="G26" s="17">
         <f>G25/G7</f>
-        <v>0.18839830345266431</v>
+        <v>0.15773932123997667</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
@@ -3963,23 +3959,23 @@
       </c>
       <c r="C27" s="14">
         <f>C25</f>
-        <v>3141.1790400000009</v>
+        <v>2625.2732200000032</v>
       </c>
       <c r="D27" s="14">
         <f>C27+D25</f>
-        <v>9727.1562527999995</v>
+        <v>7786.0491155200034</v>
       </c>
       <c r="E27" s="14">
         <f>D27+E25</f>
-        <v>19431.863145215997</v>
+        <v>15795.458198147206</v>
       </c>
       <c r="F27" s="14">
         <f>E27+F25</f>
-        <v>32512.078838065914</v>
+        <v>26923.516410283715</v>
       </c>
       <c r="G27" s="14">
         <f>F27+G25</f>
-        <v>48461.605069509998</v>
+        <v>40682.163922877538</v>
       </c>
     </row>
   </sheetData>
@@ -4004,12 +4000,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="54" t="s">
         <v>181</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="12" t="s">
@@ -4031,7 +4027,7 @@
       </c>
       <c r="C5" s="37">
         <f>WACC!C24</f>
-        <v>0.13789625369489783</v>
+        <v>0.1378818853617787</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>186</v>
@@ -4043,15 +4039,15 @@
       </c>
       <c r="C7" s="29">
         <f>Projections!C25</f>
-        <v>3141.1790400000009</v>
+        <v>2625.2732200000032</v>
       </c>
       <c r="D7" s="38">
-        <f>1/(1+$C$5)^1</f>
-        <v>0.87881473970308754</v>
+        <f>1/(1+$C$5)^0.5</f>
+        <v>0.93745711194026649</v>
       </c>
       <c r="E7" s="39">
         <f>C7*D7</f>
-        <v>2760.514440398395</v>
+        <v>2461.081050875327</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -4060,15 +4056,15 @@
       </c>
       <c r="C8" s="29">
         <f>Projections!D25</f>
-        <v>6585.9772127999977</v>
+        <v>5160.7758955199997</v>
       </c>
       <c r="D8" s="38">
-        <f>1/(1+$C$5)^2</f>
-        <v>0.77231534671940538</v>
+        <f>1/(1+$C$5)^1.5</f>
+        <v>0.82386153079694302</v>
       </c>
       <c r="E8" s="39">
         <f>C8*D8</f>
-        <v>5086.4512745897337</v>
+        <v>4251.7647293830714</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
@@ -4077,15 +4073,15 @@
       </c>
       <c r="C9" s="29">
         <f>Projections!E25</f>
-        <v>9704.7068924159994</v>
+        <v>8009.4090826272022</v>
       </c>
       <c r="D9" s="38">
-        <f>1/(1+$C$5)^3</f>
-        <v>0.67872211039591412</v>
+        <f>1/(1+$C$5)^2.5</f>
+        <v>0.72403079915012791</v>
       </c>
       <c r="E9" s="39">
         <f>C9*D9</f>
-        <v>6586.7991427943607</v>
+        <v>5799.0588588148657</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
@@ -4094,15 +4090,15 @@
       </c>
       <c r="C10" s="29">
         <f>Projections!F25</f>
-        <v>13080.215692849917</v>
+        <v>11128.05821213651</v>
       </c>
       <c r="D10" s="38">
-        <f>1/(1+$C$5)^4</f>
-        <v>0.59647099477831544</v>
+        <f>1/(1+$C$5)^3.5</f>
+        <v>0.63629697287950882</v>
       </c>
       <c r="E10" s="39">
         <f>C10*D10</f>
-        <v>7801.9692662291227</v>
+        <v>7080.7497544094203</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
@@ -4111,15 +4107,15 @@
       </c>
       <c r="C11" s="29">
         <f>Projections!G25</f>
-        <v>15949.526231444086</v>
+        <v>13758.647512593823</v>
       </c>
       <c r="D11" s="38">
-        <f>1/(1+$C$5)^5</f>
-        <v>0.52418750201654685</v>
+        <f>1/(1+$C$5)^4.5</f>
+        <v>0.55919421959793669</v>
       </c>
       <c r="E11" s="39">
         <f>C11*D11</f>
-        <v>8360.5423136080644</v>
+        <v>7693.7561585279955</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
@@ -4130,16 +4126,16 @@
       <c r="D13" s="40"/>
       <c r="E13" s="31">
         <f>SUM(E7:E11)</f>
-        <v>30596.276437619676</v>
+        <v>27286.410552010679</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="55" t="s">
+      <c r="B15" s="56" t="s">
         <v>134</v>
       </c>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
@@ -4147,7 +4143,7 @@
       </c>
       <c r="C16" s="29">
         <f>C11</f>
-        <v>15949.526231444086</v>
+        <v>13758.647512593823</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
@@ -4156,7 +4152,7 @@
       </c>
       <c r="C17" s="28">
         <f>Assumptions!C45</f>
-        <v>0.03</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
@@ -4165,7 +4161,7 @@
       </c>
       <c r="C18" s="39">
         <f>C16*(1+C17)/(C5-C17)</f>
-        <v>152257.48305257657</v>
+        <v>124932.47836188026</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>196</v>
@@ -4177,7 +4173,7 @@
       </c>
       <c r="C19" s="38">
         <f>D11</f>
-        <v>0.52418750201654685</v>
+        <v>0.55919421959793669</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
@@ -4186,16 +4182,16 @@
       </c>
       <c r="C20" s="31">
         <f>C18*C19</f>
-        <v>79811.469704656833</v>
+        <v>69861.519740007745</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="55" t="s">
+      <c r="B22" s="56" t="s">
         <v>199</v>
       </c>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
@@ -4203,7 +4199,7 @@
       </c>
       <c r="C23" s="29">
         <f>E13</f>
-        <v>30596.276437619676</v>
+        <v>27286.410552010679</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
@@ -4212,7 +4208,7 @@
       </c>
       <c r="C24" s="29">
         <f>C20</f>
-        <v>79811.469704656833</v>
+        <v>69861.519740007745</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
@@ -4232,7 +4228,7 @@
       </c>
       <c r="C26" s="43">
         <f>C23+C24+C25</f>
-        <v>110407.7461422765</v>
+        <v>97147.930292018427</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
@@ -4265,7 +4261,7 @@
       </c>
       <c r="C30" s="44">
         <f>C26</f>
-        <v>110407.7461422765</v>
+        <v>97147.930292018427</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
@@ -4283,7 +4279,7 @@
       </c>
       <c r="C33" s="43">
         <f>C26-C28+C29</f>
-        <v>117709.7461422765</v>
+        <v>104449.93029201843</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
@@ -4292,7 +4288,7 @@
       </c>
       <c r="C35" s="29">
         <f>Assumptions!C41</f>
-        <v>1636</v>
+        <v>1796</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>211</v>
@@ -4304,7 +4300,7 @@
       </c>
       <c r="C36" s="46">
         <f>C33/C35</f>
-        <v>71.949722580853603</v>
+        <v>58.15697677729311</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.25">
@@ -4321,7 +4317,7 @@
       </c>
       <c r="C39" s="48">
         <f>C36/C38-1</f>
-        <v>-0.69606842148923409</v>
+        <v>-0.75433203743803867</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.25">
@@ -4331,27 +4327,27 @@
     </row>
     <row r="42" spans="2:5" ht="24" x14ac:dyDescent="0.25">
       <c r="B42" s="9" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43" spans="2:5" ht="24" x14ac:dyDescent="0.25">
       <c r="B43" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="44" spans="2:5" ht="24" x14ac:dyDescent="0.25">
       <c r="B44" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="45" spans="2:5" ht="24" x14ac:dyDescent="0.25">
       <c r="B45" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" spans="2:5" ht="24" x14ac:dyDescent="0.25">
       <c r="B46" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -4375,30 +4371,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="56" t="s">
-        <v>221</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
+      <c r="B2" s="54" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
     </row>
     <row r="4" spans="2:9" ht="36" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="24" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" s="49">
         <v>0.02</v>
@@ -4422,23 +4418,23 @@
       </c>
       <c r="C8" s="51">
         <f>(((Projections!C25/(1+$B8)^1+Projections!D25/(1+$B8)^2+Projections!E25/(1+$B8)^3+Projections!F25/(1+$B8)^4+Projections!G25/(1+$B8)^5)+((Projections!G25*(1+C$7)/($B8-C$7))/(1+$B8)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>90.420451468856612</v>
+        <v>71.127654542827699</v>
       </c>
       <c r="D8" s="51">
         <f>(((Projections!C25/(1+$B8)^1+Projections!D25/(1+$B8)^2+Projections!E25/(1+$B8)^3+Projections!F25/(1+$B8)^4+Projections!G25/(1+$B8)^5)+((Projections!G25*(1+D$7)/($B8-D$7))/(1+$B8)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>94.61785904336098</v>
+        <v>74.425923491576754</v>
       </c>
       <c r="E8" s="51">
         <f>(((Projections!C25/(1+$B8)^1+Projections!D25/(1+$B8)^2+Projections!E25/(1+$B8)^3+Projections!F25/(1+$B8)^4+Projections!G25/(1+$B8)^5)+((Projections!G25*(1+E$7)/($B8-E$7))/(1+$B8)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>99.339942564678381</v>
+        <v>78.13647605891947</v>
       </c>
       <c r="F8" s="51">
         <f>(((Projections!C25/(1+$B8)^1+Projections!D25/(1+$B8)^2+Projections!E25/(1+$B8)^3+Projections!F25/(1+$B8)^4+Projections!G25/(1+$B8)^5)+((Projections!G25*(1+F$7)/($B8-F$7))/(1+$B8)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>104.69163722217145</v>
+        <v>82.341768968574556</v>
       </c>
       <c r="G8" s="51">
         <f>(((Projections!C25/(1+$B8)^1+Projections!D25/(1+$B8)^2+Projections!E25/(1+$B8)^3+Projections!F25/(1+$B8)^4+Projections!G25/(1+$B8)^5)+((Projections!G25*(1+G$7)/($B8-G$7))/(1+$B8)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>110.80785968787784</v>
+        <v>87.147818008180337</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
@@ -4447,23 +4443,23 @@
       </c>
       <c r="C9" s="51">
         <f>(((Projections!C25/(1+$B9)^1+Projections!D25/(1+$B9)^2+Projections!E25/(1+$B9)^3+Projections!F25/(1+$B9)^4+Projections!G25/(1+$B9)^5)+((Projections!G25*(1+C$7)/($B9-C$7))/(1+$B9)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>80.647542600501737</v>
+        <v>63.458711878232656</v>
       </c>
       <c r="D9" s="51">
         <f>(((Projections!C25/(1+$B9)^1+Projections!D25/(1+$B9)^2+Projections!E25/(1+$B9)^3+Projections!F25/(1+$B9)^4+Projections!G25/(1+$B9)^5)+((Projections!G25*(1+D$7)/($B9-D$7))/(1+$B9)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>83.908452477632991</v>
+        <v>66.021092967393642</v>
       </c>
       <c r="E9" s="51">
         <f>(((Projections!C25/(1+$B9)^1+Projections!D25/(1+$B9)^2+Projections!E25/(1+$B9)^3+Projections!F25/(1+$B9)^4+Projections!G25/(1+$B9)^5)+((Projections!G25*(1+E$7)/($B9-E$7))/(1+$B9)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>87.531685674445512</v>
+        <v>68.868183066461455</v>
       </c>
       <c r="F9" s="51">
         <f>(((Projections!C25/(1+$B9)^1+Projections!D25/(1+$B9)^2+Projections!E25/(1+$B9)^3+Projections!F25/(1+$B9)^4+Projections!G25/(1+$B9)^5)+((Projections!G25*(1+F$7)/($B9-F$7))/(1+$B9)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>91.581181600294769</v>
+        <v>72.050224941890164</v>
       </c>
       <c r="G9" s="51">
         <f>(((Projections!C25/(1+$B9)^1+Projections!D25/(1+$B9)^2+Projections!E25/(1+$B9)^3+Projections!F25/(1+$B9)^4+Projections!G25/(1+$B9)^5)+((Projections!G25*(1+G$7)/($B9-G$7))/(1+$B9)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>96.136864516875207</v>
+        <v>75.630022051747474</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
@@ -4472,23 +4468,23 @@
       </c>
       <c r="C10" s="51">
         <f>(((Projections!C25/(1+$B10)^1+Projections!D25/(1+$B10)^2+Projections!E25/(1+$B10)^3+Projections!F25/(1+$B10)^4+Projections!G25/(1+$B10)^5)+((Projections!G25*(1+C$7)/($B10-C$7))/(1+$B10)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>72.68725828980125</v>
+        <v>57.213764018722856</v>
       </c>
       <c r="D10" s="51">
         <f>(((Projections!C25/(1+$B10)^1+Projections!D25/(1+$B10)^2+Projections!E25/(1+$B10)^3+Projections!F25/(1+$B10)^4+Projections!G25/(1+$B10)^5)+((Projections!G25*(1+D$7)/($B10-D$7))/(1+$B10)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>75.275702053854133</v>
+        <v>59.247729875271077</v>
       </c>
       <c r="E10" s="51">
         <f>(((Projections!C25/(1+$B10)^1+Projections!D25/(1+$B10)^2+Projections!E25/(1+$B10)^3+Projections!F25/(1+$B10)^4+Projections!G25/(1+$B10)^5)+((Projections!G25*(1+E$7)/($B10-E$7))/(1+$B10)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>78.122990194312322</v>
+        <v>61.485092317474148</v>
       </c>
       <c r="F10" s="51">
         <f>(((Projections!C25/(1+$B10)^1+Projections!D25/(1+$B10)^2+Projections!E25/(1+$B10)^3+Projections!F25/(1+$B10)^4+Projections!G25/(1+$B10)^5)+((Projections!G25*(1+F$7)/($B10-F$7))/(1+$B10)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>81.269992875871353</v>
+        <v>63.957966595698579</v>
       </c>
       <c r="G10" s="51">
         <f>(((Projections!C25/(1+$B10)^1+Projections!D25/(1+$B10)^2+Projections!E25/(1+$B10)^3+Projections!F25/(1+$B10)^4+Projections!G25/(1+$B10)^5)+((Projections!G25*(1+G$7)/($B10-G$7))/(1+$B10)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>84.766662522048094</v>
+        <v>66.705604682614634</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
@@ -4497,23 +4493,23 @@
       </c>
       <c r="C11" s="51">
         <f>(((Projections!C25/(1+$B11)^1+Projections!D25/(1+$B11)^2+Projections!E25/(1+$B11)^3+Projections!F25/(1+$B11)^4+Projections!G25/(1+$B11)^5)+((Projections!G25*(1+C$7)/($B11-C$7))/(1+$B11)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>66.084996070872222</v>
+        <v>52.035604751265147</v>
       </c>
       <c r="D11" s="51">
         <f>(((Projections!C25/(1+$B11)^1+Projections!D25/(1+$B11)^2+Projections!E25/(1+$B11)^3+Projections!F25/(1+$B11)^4+Projections!G25/(1+$B11)^5)+((Projections!G25*(1+D$7)/($B11-D$7))/(1+$B11)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>68.176390758125606</v>
+        <v>53.678995828759241</v>
       </c>
       <c r="E11" s="51">
         <f>(((Projections!C25/(1+$B11)^1+Projections!D25/(1+$B11)^2+Projections!E25/(1+$B11)^3+Projections!F25/(1+$B11)^4+Projections!G25/(1+$B11)^5)+((Projections!G25*(1+E$7)/($B11-E$7))/(1+$B11)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>70.457912235129328</v>
+        <v>55.471786095116457</v>
       </c>
       <c r="F11" s="51">
         <f>(((Projections!C25/(1+$B11)^1+Projections!D25/(1+$B11)^2+Projections!E25/(1+$B11)^3+Projections!F25/(1+$B11)^4+Projections!G25/(1+$B11)^5)+((Projections!G25*(1+F$7)/($B11-F$7))/(1+$B11)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>72.956721471847672</v>
+        <v>57.435318291602933</v>
       </c>
       <c r="G11" s="51">
         <f>(((Projections!C25/(1+$B11)^1+Projections!D25/(1+$B11)^2+Projections!E25/(1+$B11)^3+Projections!F25/(1+$B11)^4+Projections!G25/(1+$B11)^5)+((Projections!G25*(1+G$7)/($B11-G$7))/(1+$B11)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>75.705411632237869</v>
+        <v>59.595203707738051</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
@@ -4522,23 +4518,23 @@
       </c>
       <c r="C12" s="51">
         <f>(((Projections!C25/(1+$B12)^1+Projections!D25/(1+$B12)^2+Projections!E25/(1+$B12)^3+Projections!F25/(1+$B12)^4+Projections!G25/(1+$B12)^5)+((Projections!G25*(1+C$7)/($B12-C$7))/(1+$B12)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>60.526103016747847</v>
+        <v>47.676997656798918</v>
       </c>
       <c r="D12" s="51">
         <f>(((Projections!C25/(1+$B12)^1+Projections!D25/(1+$B12)^2+Projections!E25/(1+$B12)^3+Projections!F25/(1+$B12)^4+Projections!G25/(1+$B12)^5)+((Projections!G25*(1+D$7)/($B12-D$7))/(1+$B12)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>62.241204274693935</v>
+        <v>49.02470219171343</v>
       </c>
       <c r="E12" s="51">
         <f>(((Projections!C25/(1+$B12)^1+Projections!D25/(1+$B12)^2+Projections!E25/(1+$B12)^3+Projections!F25/(1+$B12)^4+Projections!G25/(1+$B12)^5)+((Projections!G25*(1+E$7)/($B12-E$7))/(1+$B12)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>64.099230637468864</v>
+        <v>50.48471543787084</v>
       </c>
       <c r="F12" s="51">
         <f>(((Projections!C25/(1+$B12)^1+Projections!D25/(1+$B12)^2+Projections!E25/(1+$B12)^3+Projections!F25/(1+$B12)^4+Projections!G25/(1+$B12)^5)+((Projections!G25*(1+F$7)/($B12-F$7))/(1+$B12)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>66.118824510050317</v>
+        <v>52.071686357607135</v>
       </c>
       <c r="G12" s="51">
         <f>(((Projections!C25/(1+$B12)^1+Projections!D25/(1+$B12)^2+Projections!E25/(1+$B12)^3+Projections!F25/(1+$B12)^4+Projections!G25/(1+$B12)^5)+((Projections!G25*(1+G$7)/($B12-G$7))/(1+$B12)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>68.322017825593733</v>
+        <v>53.80292736095582</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
@@ -4547,46 +4543,46 @@
       </c>
       <c r="C13" s="51">
         <f>(((Projections!C25/(1+$B13)^1+Projections!D25/(1+$B13)^2+Projections!E25/(1+$B13)^3+Projections!F25/(1+$B13)^4+Projections!G25/(1+$B13)^5)+((Projections!G25*(1+C$7)/($B13-C$7))/(1+$B13)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>55.78588956720985</v>
+        <v>43.961397664288675</v>
       </c>
       <c r="D13" s="51">
         <f>(((Projections!C25/(1+$B13)^1+Projections!D25/(1+$B13)^2+Projections!E25/(1+$B13)^3+Projections!F25/(1+$B13)^4+Projections!G25/(1+$B13)^5)+((Projections!G25*(1+D$7)/($B13-D$7))/(1+$B13)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>57.210318318622782</v>
+        <v>45.080695477783813</v>
       </c>
       <c r="E13" s="51">
         <f>(((Projections!C25/(1+$B13)^1+Projections!D25/(1+$B13)^2+Projections!E25/(1+$B13)^3+Projections!F25/(1+$B13)^4+Projections!G25/(1+$B13)^5)+((Projections!G25*(1+E$7)/($B13-E$7))/(1+$B13)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>58.744318512452104</v>
+        <v>46.286093123086282</v>
       </c>
       <c r="F13" s="51">
         <f>(((Projections!C25/(1+$B13)^1+Projections!D25/(1+$B13)^2+Projections!E25/(1+$B13)^3+Projections!F25/(1+$B13)^4+Projections!G25/(1+$B13)^5)+((Projections!G25*(1+F$7)/($B13-F$7))/(1+$B13)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>60.401038721787749</v>
+        <v>47.587922580012943</v>
       </c>
       <c r="G13" s="51">
         <f>(((Projections!C25/(1+$B13)^1+Projections!D25/(1+$B13)^2+Projections!E25/(1+$B13)^3+Projections!F25/(1+$B13)^4+Projections!G25/(1+$B13)^5)+((Projections!G25*(1+G$7)/($B13-G$7))/(1+$B13)^5))-Assumptions!C39+Assumptions!C40)/Assumptions!C41</f>
-        <v>62.195818948568053</v>
+        <v>48.998237825016822</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C14" s="37">
         <f>WACC!C24</f>
-        <v>0.13789625369489783</v>
+        <v>0.1378818853617787</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E14" s="48">
         <f>Assumptions!C45</f>
-        <v>0.03</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G14" s="52">
         <f>'DCF Valuation'!C36</f>
-        <v>71.949722580853603</v>
+        <v>58.15697677729311</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
@@ -4596,17 +4592,17 @@
     </row>
     <row r="17" spans="2:2" ht="36" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="36" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="36" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
